--- a/human_validation/judge/kor/judge_D002_S002_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S002_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 위생 절차나 배치 작업일지, 라인 마감 서류 작업을 시작은 하는데, 어쩐지 마지막 부분을 빼먹게 돼요. 일 때문에 제대로 끝까지 마쳐야 한다는 걸 아는데도, 끝까지 다 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 일을 끝까지 마무리하기 어려운 게 얼마나 오래되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 정육 가공 일을 정규직으로 시작한 이후로 심각해졌어요, 한 2년 4개월 정도 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 어렸을 때도 이렇게 학교 숙제나 집안일을 끝까지 마치는 데 어려움을 겪으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 저희 엄마가 아직도 4학년 때쯤 성적표를 가지고 계신데, 제가 똑똑하긴 한데 수업 과제를 끝내고 숙제를 내려면 계속 알려줘야 한다고 적혀 있었어요. 수업 내용은 이해했는데, 선생님이 바로 옆에서 챙겨주지 않으면 지시사항 일부를 놓치곤 했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 일을 끝까지 마치기 어려운 것 외에, 지속적으로 기분이 가라앉거나 우울하다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 계속 기분이 가라앉는다고 느낀 적은 딱히 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 뚜렷한 이유가 없는데도 여러 가지 일에 대해 지나치게 걱정하는 경우가 자주 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그런 것 같지 않아요. 그러니까, 가끔 이런저런 일들을 걱정하긴 하는데, 이유 없이 여러 가지를 계속 걱정하는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)
 인구통계: 성별 여성 / 나이 21 / 직업상태 butcher or meat poultry or fish processing worker / 최종학력 학사
@@ -575,182 +684,36 @@
 증상 지속 기간: 2 years and 4 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S004
-배경 서술: 클라라는 대학 생활과 푸드 뱅크 봉사 위주의 삶에서 정육 가공 정규직으로 전환하면서, 업무 속도와 안전 문서 작업, 단계별 절차들이 그동안 그녀가 근무 시간 내내 유지해 본 적 없는 수준의 지속적인 집중력을 요구한다는 것을 알게 되었다. 이후 2년 4개월 동안, 그녀는 반복적인 절단 작업과 보고 업무 중 집중력을 유지하지 못하는 일이 점점 늘어났고, 상사의 직접적인 지시를 제대로 받아들이지 못하는 것처럼 보였으며, 필수 작업일지와 마무리 청소 절차를 완료하지 못하고, 장시간 독해가 필요한 자격 인증 모듈 학습을 피하고, 필수 도구와 보호 장비를 자주 잃어버렸다. 의욕과 기술적 능력이 있었음에도 불구하고 이러한 패턴은 심각한 직무상 장애를 초래했고, 여러 차례의 공식 재교육 면담 끝에 그녀는 산업보건 의뢰에 동의했고, 이는 정신과 진료로 이어졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 위생 절차나 배치 작업일지, 라인 마감 서류 작업을 시작은 하는데, 어쩐지 마지막 부분을 빼먹게 돼요. 일 때문에 제대로 끝까지 마쳐야 한다는 걸 아는데도, 끝까지 다 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 일을 끝까지 마무리하기 어려운 게 얼마나 오래되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 정육 가공 일을 정규직으로 시작한 이후로 심각해졌어요, 한 2년 4개월 정도 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 어렸을 때도 이렇게 학교 숙제나 집안일을 끝까지 마치는 데 어려움을 겪으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 저희 엄마가 아직도 4학년 때쯤 성적표를 가지고 계신데, 제가 똑똑하긴 한데 수업 과제를 끝내고 숙제를 내려면 계속 알려줘야 한다고 적혀 있었어요. 수업 내용은 이해했는데, 선생님이 바로 옆에서 챙겨주지 않으면 지시사항 일부를 놓치곤 했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 일을 끝까지 마치기 어려운 것 외에, 지속적으로 기분이 가라앉거나 우울하다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 계속 기분이 가라앉는다고 느낀 적은 딱히 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 뚜렷한 이유가 없는데도 여러 가지 일에 대해 지나치게 걱정하는 경우가 자주 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그런 것 같지 않아요. 그러니까, 가끔 이런저런 일들을 걱정하긴 하는데, 이유 없이 여러 가지를 계속 걱정하는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 클라라는 대학 생활과 푸드 뱅크 봉사 위주의 삶에서 정육 가공 정규직으로 전환하면서, 업무 속도와 안전 문서 작업, 단계별 절차들이 그동안 그녀가 근무 시간 내내 유지해 본 적 없는 수준의 지속적인 집중력을 요구한다는 것을 알게 되었다. 이후 2년 4개월 동안, 그녀는 반복적인 절단 작업과 보고 업무 중 집중력을 유지하지 못하는 일이 점점 늘어났고, 상사의 직접적인 지시를 제대로 받아들이지 못하는 것처럼 보였으며, 필수 작업일지와 마무리 청소 절차를 완료하지 못하고, 장시간 독해가 필요한 자격 인증 모듈 학습을 피하고, 필수 도구와 보호 장비를 자주 잃어버렸다. 의욕과 기술적 능력이 있었음에도 불구하고 이러한 패턴은 심각한 직무상 장애를 초래했고, 여러 차례의 공식 재교육 면담 끝에 그녀는 산업보건 의뢰에 동의했고, 이는 정신과 진료로 이어졌다.
+표집된 증상 목록:
+  - S002 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - S003 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
+  - S004 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - S006 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.
+  - S007 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
-  누락: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S002_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S002_P003__gemini-3.8-flash_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -709,11 +714,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S002_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S002_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2138</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
